--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="95">
   <si>
     <t>Property</t>
   </si>
@@ -31,13 +31,16 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:2.16.840.1.113883.6.347</t>
+    <t>OID:2.16.840.1.113883.6.347 (use: usual, )</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-cim11-mms (use: secondary, )</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2024-01</t>
+    <t>2025-01</t>
   </si>
   <si>
     <t>Name</t>
@@ -49,7 +52,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Classification internationale des maladies (11eme révision). Linéarisation pour les statistiques de morbi-mortalité</t>
+    <t>Classification internationale des maladies et des problèmes de santé connexes - 11ème révision</t>
   </si>
   <si>
     <t>Status</t>
@@ -67,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T16:58:25+00:00</t>
+    <t>2025-02-25T17:04:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>35417</t>
+    <t>36155</t>
   </si>
   <si>
     <t>Code</t>
@@ -429,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -462,65 +465,67 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>6</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>8</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -544,15 +549,15 @@
       <c r="A15" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -570,22 +575,28 @@
       <c r="A19" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B19" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B21" t="s" s="2">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>33</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -600,298 +611,298 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -906,13 +917,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -920,38 +931,38 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T17:04:42+00:00</t>
+    <t>2025-02-26T16:08:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T16:08:18+00:00</t>
+    <t>2025-02-27T08:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T08:43:40+00:00</t>
+    <t>2025-02-27T14:19:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:19:46+00:00</t>
+    <t>2025-03-07T08:37:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T08:37:17+00:00</t>
+    <t>2025-03-11T13:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:02:31+00:00</t>
+    <t>2025-03-14T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T12:41:19+00:00</t>
+    <t>2025-03-25T09:33:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T09:33:15+00:00</t>
+    <t>2025-05-19T13:21:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T13:21:22+00:00</t>
+    <t>2025-06-03T15:31:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-03T15:31:08+00:00</t>
+    <t>2025-06-03T16:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-03T16:16:13+00:00</t>
+    <t>2025-06-04T08:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T08:06:36+00:00</t>
+    <t>2025-06-04T14:37:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T14:37:49+00:00</t>
+    <t>2025-06-04T15:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T15:14:11+00:00</t>
+    <t>2025-06-11T10:56:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T10:56:37+00:00</t>
+    <t>2025-06-11T12:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T12:34:17+00:00</t>
+    <t>2025-06-11T14:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T14:35:18+00:00</t>
+    <t>2025-06-12T14:08:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12T14:08:06+00:00</t>
+    <t>2025-06-16T10:40:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T10:40:18+00:00</t>
+    <t>2025-06-16T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T15:31:48+00:00</t>
+    <t>2025-06-17T11:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-17T11:26:30+00:00</t>
+    <t>2025-06-18T08:23:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-18T08:23:39+00:00</t>
+    <t>2025-06-18T10:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-18T10:20:00+00:00</t>
+    <t>2025-06-19T11:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-19T11:33:33+00:00</t>
+    <t>2025-06-19T12:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-19T12:18:09+00:00</t>
+    <t>2025-06-19T14:16:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-19T14:16:36+00:00</t>
+    <t>2025-06-23T13:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T13:32:18+00:00</t>
+    <t>2025-06-30T12:13:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-30T12:13:52+00:00</t>
+    <t>2025-07-02T12:17:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-02T12:17:31+00:00</t>
+    <t>2025-07-02T14:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-02T14:11:11+00:00</t>
+    <t>2025-07-08T14:18:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T14:18:27+00:00</t>
+    <t>2025-07-11T07:31:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T07:31:28+00:00</t>
+    <t>2025-07-11T10:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-11T10:08:59+00:00</t>
+    <t>2025-07-16T12:42:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T12:42:07+00:00</t>
+    <t>2025-07-16T15:09:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T15:09:46+00:00</t>
+    <t>2025-07-17T14:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-17T14:23:37+00:00</t>
+    <t>2025-07-18T07:52:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-18T07:52:12+00:00</t>
+    <t>2025-07-28T09:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-28T09:55:12+00:00</t>
+    <t>2025-07-28T16:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-28T16:12:17+00:00</t>
+    <t>2025-07-30T09:57:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:57:17+00:00</t>
+    <t>2025-09-04T08:14:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-04T08:14:57+00:00</t>
+    <t>2025-09-18T06:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T06:32:12+00:00</t>
+    <t>2025-09-18T11:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T11:04:21+00:00</t>
+    <t>2025-09-18T14:06:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T14:06:27+00:00</t>
+    <t>2025-09-18T16:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T16:36:10+00:00</t>
+    <t>2025-10-13T09:02:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T09:02:22+00:00</t>
+    <t>2025-10-13T11:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T11:17:15+00:00</t>
+    <t>2025-10-13T12:32:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T12:32:46+00:00</t>
+    <t>2025-10-13T13:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T13:38:16+00:00</t>
+    <t>2025-10-13T14:51:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T14:51:45+00:00</t>
+    <t>2025-10-14T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T07:40:12+00:00</t>
+    <t>2025-10-14T09:41:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T09:41:04+00:00</t>
+    <t>2025-10-14T11:48:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T11:48:11+00:00</t>
+    <t>2025-10-14T13:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T13:06:01+00:00</t>
+    <t>2025-10-14T14:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T14:12:23+00:00</t>
+    <t>2025-10-14T15:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T15:10:58+00:00</t>
+    <t>2025-10-14T17:45:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-14T17:45:09+00:00</t>
+    <t>2025-10-15T07:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-15T07:59:39+00:00</t>
+    <t>2025-10-15T12:33:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-15T12:33:07+00:00</t>
+    <t>2025-10-15T13:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-15T13:56:08+00:00</t>
+    <t>2025-10-29T16:41:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T16:41:38+00:00</t>
+    <t>2025-10-31T08:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T08:16:32+00:00</t>
+    <t>2025-11-03T20:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-03T20:06:17+00:00</t>
+    <t>2025-11-04T18:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-04T18:14:37+00:00</t>
+    <t>2025-11-04T21:20:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-04T21:20:50+00:00</t>
+    <t>2025-11-05T09:19:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T09:19:17+00:00</t>
+    <t>2025-11-05T12:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T12:12:06+00:00</t>
+    <t>2025-11-05T14:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T14:25:10+00:00</t>
+    <t>2025-11-07T09:51:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T09:51:42+00:00</t>
+    <t>2025-11-07T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T14:39:45+00:00</t>
+    <t>2025-11-07T16:06:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T16:06:45+00:00</t>
+    <t>2025-11-12T17:02:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T17:02:37+00:00</t>
+    <t>2025-11-12T18:15:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:15:08+00:00</t>
+    <t>2025-11-20T16:01:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T16:01:06+00:00</t>
+    <t>2025-11-26T08:37:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-26T08:37:36+00:00</t>
+    <t>2025-11-27T08:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T08:43:00+00:00</t>
+    <t>2025-11-28T09:15:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T09:15:19+00:00</t>
+    <t>2025-11-28T13:41:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T13:41:04+00:00</t>
+    <t>2025-12-08T15:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08T15:29:34+00:00</t>
+    <t>2025-12-08T17:18:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08T17:18:19+00:00</t>
+    <t>2025-12-10T13:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T13:53:18+00:00</t>
+    <t>2025-12-11T13:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T13:50:41+00:00</t>
+    <t>2025-12-15T15:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T15:13:27+00:00</t>
+    <t>2025-12-20T13:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-20T13:25:39+00:00</t>
+    <t>2026-01-07T09:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T09:16:12+00:00</t>
+    <t>2026-01-08T09:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T09:55:22+00:00</t>
+    <t>2026-01-15T10:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-01</t>
+    <t>2026-02</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T10:06:16+00:00</t>
+    <t>2026-03-09T11:39:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>36155</t>
+    <t>36480</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:39:04+00:00</t>
+    <t>2026-03-10T13:56:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T13:56:55+00:00</t>
+    <t>2026-03-13T11:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T11:12:59+00:00</t>
+    <t>2026-03-13T14:08:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:07+00:00</t>
+    <t>2026-03-16T09:36:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T09:36:58+00:00</t>
+    <t>2026-04-15T12:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:25:44+00:00</t>
+    <t>2026-04-21T11:09:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:09:45+00:00</t>
+    <t>2026-04-21T12:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T12:38:05+00:00</t>
+    <t>2026-04-21T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:44:55+00:00</t>
+    <t>2026-04-21T15:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T15:54:01+00:00</t>
+    <t>2026-04-22T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:26+00:00</t>
+    <t>2026-04-23T19:56:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T19:56:15+00:00</t>
+    <t>2026-04-24T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T09:23:28+00:00</t>
+    <t>2026-04-27T15:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T15:12:13+00:00</t>
+    <t>2026-05-12T11:56:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:56:23+00:00</t>
+    <t>2026-05-12T13:38:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T13:38:44+00:00</t>
+    <t>2026-05-12T15:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T15:57:24+00:00</t>
+    <t>2026-05-12T16:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:58:28+00:00</t>
+    <t>2026-05-12T20:14:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T20:14:18+00:00</t>
+    <t>2026-05-13T09:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T09:41:30+00:00</t>
+    <t>2026-05-13T10:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T10:55:41+00:00</t>
+    <t>2026-05-18T13:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T13:45:33+00:00</t>
+    <t>2026-06-18T15:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T15:03:25+00:00</t>
+    <t>2026-06-21T11:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T11:24:04+00:00</t>
+    <t>2026-06-21T12:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T12:13:53+00:00</t>
+    <t>2026-06-21T13:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T13:26:08+00:00</t>
+    <t>2026-06-21T14:37:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T14:37:12+00:00</t>
+    <t>2026-06-21T15:36:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T15:36:29+00:00</t>
+    <t>2026-06-21T17:31:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T17:31:55+00:00</t>
+    <t>2026-06-21T18:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T18:39:37+00:00</t>
+    <t>2026-06-21T21:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:38:11+00:00</t>
+    <t>2026-06-22T02:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T02:12:35+00:00</t>
+    <t>2026-06-22T06:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T06:15:53+00:00</t>
+    <t>2026-06-22T09:45:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:45:10+00:00</t>
+    <t>2026-06-22T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:12:12+00:00</t>
+    <t>2026-06-22T20:46:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T20:46:27+00:00</t>
+    <t>2026-06-23T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T17:00:44+00:00</t>
+    <t>2026-06-24T07:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:19:56+00:00</t>
+    <t>2026-06-24T08:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:50:58+00:00</t>
+    <t>2026-06-24T10:14:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:14:00+00:00</t>
+    <t>2026-06-24T11:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T11:43:48+00:00</t>
+    <t>2026-06-24T13:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-cim11-mms.xlsx
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:47:07+00:00</t>
+    <t>2026-06-24T15:18:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
